--- a/forms/trg/Formulir_TRG_urbinfrastructur-r.xlsx
+++ b/forms/trg/Formulir_TRG_urbinfrastructur-r.xlsx
@@ -916,7 +916,11 @@
           <t>Evi Aprianti, PhD</t>
         </is>
       </c>
-      <c r="C5" s="12" t="n"/>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>Leader</t>
+        </is>
+      </c>
       <c r="D5" s="12" t="n"/>
       <c r="E5" s="11" t="inlineStr">
         <is>
@@ -947,7 +951,7 @@
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="12" t="n"/>
@@ -984,7 +988,7 @@
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="12" t="n"/>
@@ -1017,7 +1021,7 @@
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="12" t="n"/>
@@ -1050,7 +1054,7 @@
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D9" s="12" t="n"/>
@@ -1083,7 +1087,7 @@
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D10" s="12" t="n"/>
@@ -1116,7 +1120,7 @@
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D11" s="12" t="n"/>
@@ -1149,7 +1153,7 @@
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D12" s="12" t="n"/>
@@ -1182,7 +1186,7 @@
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D13" s="12" t="n"/>
@@ -1215,7 +1219,7 @@
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D14" s="12" t="n"/>
